--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,13 +672,18 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688124</v>
+        <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92083</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414613</v>
+        <v>414506</v>
       </c>
       <c r="R2" t="n">
-        <v>6840353</v>
+        <v>6840350</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,64 +775,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552358</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688126</v>
+        <v>135552345</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>92240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>72</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Urskogsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis primaeva</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>414608</v>
+        <v>414623</v>
       </c>
       <c r="R3" t="n">
-        <v>6840207</v>
+        <v>6840397</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,17 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,28 +884,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688125</v>
+        <v>135552336</v>
       </c>
       <c r="B4" t="n">
-        <v>79085</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,41 +919,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414605</v>
+        <v>414690</v>
       </c>
       <c r="R4" t="n">
-        <v>6840213</v>
+        <v>6840294</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,17 +973,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,17 +1003,6578 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552336</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135552337</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>414697</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6840323</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552337</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135552341</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>414653</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6840340</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552341</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135552346</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>414623</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6840405</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552346</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135552350</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>414609</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6840382</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552350</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135552351</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>414601</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6840335</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552351</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135552354</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>414588</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6840341</v>
+      </c>
+      <c r="S10" t="n">
+        <v>28</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552354</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135552357</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>353</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>414522</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6840327</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552357</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135552364</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>414591</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6840303</v>
+      </c>
+      <c r="S12" t="n">
+        <v>24</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552364</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135552365</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>414601</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6840307</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552365</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135552379</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>353</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>414643</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6840242</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552379</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135552390</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>414552</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6840177</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552390</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135552381</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79468</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>967</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>414671</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6840258</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552381</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129688124</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storbäcksvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>414613</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6840353</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688124</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135552349</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>414617</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6840383</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552349</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135552371</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>414590</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6840200</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552371</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135552372</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>414593</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6840201</v>
+      </c>
+      <c r="S20" t="n">
+        <v>22</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552372</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135552384</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>414637</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6840257</v>
+      </c>
+      <c r="S21" t="n">
+        <v>19</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552384</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135552385</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>414591</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6840230</v>
+      </c>
+      <c r="S22" t="n">
+        <v>49</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552385</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135552348</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>414626</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6840401</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552348</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135552342</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>414651</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6840334</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552342</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135552338</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>414675</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6840320</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552338</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135552344</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>414654</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6840390</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552344</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135552361</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>414577</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6840369</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552361</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135552366</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>414606</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6840293</v>
+      </c>
+      <c r="S28" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552366</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135552369</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>414575</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6840232</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552369</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135552376</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>414635</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6840234</v>
+      </c>
+      <c r="S30" t="n">
+        <v>14</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552376</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135552388</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>414554</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6840205</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552388</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135552394</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>414567</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6840142</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552394</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129688126</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storbäcksvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>414608</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6840207</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688126</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135552340</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>414679</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6840324</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552340</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135552347</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>414608</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6840392</v>
+      </c>
+      <c r="S35" t="n">
+        <v>14</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552347</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135552352</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>414600</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6840351</v>
+      </c>
+      <c r="S36" t="n">
+        <v>18</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552352</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135552360</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>414559</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6840378</v>
+      </c>
+      <c r="S37" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552360</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135552367</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>414590</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6840249</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552367</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135552377</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>414636</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6840234</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552377</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135552378</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>414643</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6840239</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552378</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135552380</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>414673</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6840258</v>
+      </c>
+      <c r="S41" t="n">
+        <v>24</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552380</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135552382</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>414668</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6840259</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552382</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135552362</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>414577</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6840367</v>
+      </c>
+      <c r="S43" t="n">
+        <v>9</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552362</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135552368</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>414574</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6840234</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552368</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135552387</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>414557</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6840202</v>
+      </c>
+      <c r="S45" t="n">
+        <v>17</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552387</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135552391</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>414545</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6840174</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552391</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135552393</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>414567</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6840142</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552393</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135552359</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58848</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>414524</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6840378</v>
+      </c>
+      <c r="S48" t="n">
+        <v>22</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552359</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129688125</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storbäcksvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>414605</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6840213</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688125</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135552353</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>414594</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6840343</v>
+      </c>
+      <c r="S50" t="n">
+        <v>11</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552353</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135552374</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>414602</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6840210</v>
+      </c>
+      <c r="S51" t="n">
+        <v>9</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552374</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135552375</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>414607</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6840232</v>
+      </c>
+      <c r="S52" t="n">
+        <v>22</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552375</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135552389</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>414554</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6840204</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552389</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135552339</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>414685</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6840332</v>
+      </c>
+      <c r="S54" t="n">
+        <v>16</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552339</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135552343</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>414649</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6840383</v>
+      </c>
+      <c r="S55" t="n">
+        <v>11</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552343</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135552355</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>414564</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6840341</v>
+      </c>
+      <c r="S56" t="n">
+        <v>13</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552355</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135552356</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>414524</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6840332</v>
+      </c>
+      <c r="S57" t="n">
+        <v>13</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552356</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135552363</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>414577</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6840367</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552363</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135552370</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>414573</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6840230</v>
+      </c>
+      <c r="S59" t="n">
+        <v>24</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552370</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135552373</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>414604</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6840230</v>
+      </c>
+      <c r="S60" t="n">
+        <v>16</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552373</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135552383</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>414668</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6840259</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552383</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135552392</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>414564</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6840146</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552392</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,51 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135552345</v>
+        <v>135552336</v>
       </c>
       <c r="B3" t="n">
-        <v>92240</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Urskogsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis primaeva</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>414623</v>
+        <v>414690</v>
       </c>
       <c r="R3" t="n">
-        <v>6840397</v>
+        <v>6840294</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,13 +898,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552345</t>
+          <t>https://artportalen.se/Sighting/135552336</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135552336</v>
+        <v>135552337</v>
       </c>
       <c r="B4" t="n">
         <v>79039</v>
@@ -943,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414690</v>
+        <v>414697</v>
       </c>
       <c r="R4" t="n">
-        <v>6840294</v>
+        <v>6840323</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,13 +1010,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552336</t>
+          <t>https://artportalen.se/Sighting/135552337</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135552337</v>
+        <v>135552341</v>
       </c>
       <c r="B5" t="n">
         <v>79039</v>
@@ -1055,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414697</v>
+        <v>414653</v>
       </c>
       <c r="R5" t="n">
-        <v>6840323</v>
+        <v>6840340</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,13 +1122,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552337</t>
+          <t>https://artportalen.se/Sighting/135552341</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135552341</v>
+        <v>135552346</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1167,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414653</v>
+        <v>414623</v>
       </c>
       <c r="R6" t="n">
-        <v>6840340</v>
+        <v>6840405</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,13 +1234,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552341</t>
+          <t>https://artportalen.se/Sighting/135552346</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135552346</v>
+        <v>135552350</v>
       </c>
       <c r="B7" t="n">
         <v>79039</v>
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414623</v>
+        <v>414609</v>
       </c>
       <c r="R7" t="n">
-        <v>6840405</v>
+        <v>6840382</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,13 +1346,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552346</t>
+          <t>https://artportalen.se/Sighting/135552350</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135552350</v>
+        <v>135552351</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1391,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414609</v>
+        <v>414601</v>
       </c>
       <c r="R8" t="n">
-        <v>6840382</v>
+        <v>6840335</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,13 +1458,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552350</t>
+          <t>https://artportalen.se/Sighting/135552351</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135552351</v>
+        <v>135552354</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>414601</v>
+        <v>414588</v>
       </c>
       <c r="R9" t="n">
-        <v>6840335</v>
+        <v>6840341</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,13 +1570,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552351</t>
+          <t>https://artportalen.se/Sighting/135552354</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135552354</v>
+        <v>135552357</v>
       </c>
       <c r="B10" t="n">
         <v>79039</v>
@@ -1615,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414588</v>
+        <v>414522</v>
       </c>
       <c r="R10" t="n">
-        <v>6840341</v>
+        <v>6840327</v>
       </c>
       <c r="S10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,13 +1682,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552354</t>
+          <t>https://artportalen.se/Sighting/135552357</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135552357</v>
+        <v>135552364</v>
       </c>
       <c r="B11" t="n">
         <v>79039</v>
@@ -1727,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414522</v>
+        <v>414591</v>
       </c>
       <c r="R11" t="n">
-        <v>6840327</v>
+        <v>6840303</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,13 +1794,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552357</t>
+          <t>https://artportalen.se/Sighting/135552364</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135552364</v>
+        <v>135552365</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1839,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414591</v>
+        <v>414601</v>
       </c>
       <c r="R12" t="n">
-        <v>6840303</v>
+        <v>6840307</v>
       </c>
       <c r="S12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,13 +1906,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552364</t>
+          <t>https://artportalen.se/Sighting/135552365</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135552365</v>
+        <v>135552379</v>
       </c>
       <c r="B13" t="n">
         <v>79039</v>
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414601</v>
+        <v>414643</v>
       </c>
       <c r="R13" t="n">
-        <v>6840307</v>
+        <v>6840242</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -1986,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,13 +2018,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552365</t>
+          <t>https://artportalen.se/Sighting/135552379</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135552379</v>
+        <v>135552390</v>
       </c>
       <c r="B14" t="n">
         <v>79039</v>
@@ -2063,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414643</v>
+        <v>414552</v>
       </c>
       <c r="R14" t="n">
-        <v>6840242</v>
+        <v>6840177</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,16 +2130,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552379</t>
+          <t>https://artportalen.se/Sighting/135552390</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135552390</v>
+        <v>135552381</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>967</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414552</v>
+        <v>414671</v>
       </c>
       <c r="R15" t="n">
-        <v>6840177</v>
+        <v>6840258</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,54 +2242,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552390</t>
+          <t>https://artportalen.se/Sighting/135552381</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135552381</v>
+        <v>129688124</v>
       </c>
       <c r="B16" t="n">
-        <v>79468</v>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>967</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Plantbygget, Dlr</t>
+          <t>Storbäcksvallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>414671</v>
+        <v>414613</v>
       </c>
       <c r="R16" t="n">
-        <v>6840258</v>
+        <v>6840353</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2317,22 +2317,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>21:10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>21:10</t>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,27 +2342,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552381</t>
+          <t>https://artportalen.se/Sighting/129688124</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129688124</v>
+        <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92083</v>
+        <v>92153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,21 +2387,17 @@
           <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>414613</v>
+        <v>414617</v>
       </c>
       <c r="R17" t="n">
-        <v>6840353</v>
+        <v>6840383</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2433,17 +2424,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,24 +2454,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129688124</t>
+          <t>https://artportalen.se/Sighting/135552349</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135552349</v>
+        <v>135552371</v>
       </c>
       <c r="B18" t="n">
         <v>92153</v>
@@ -2510,13 +2506,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>414617</v>
+        <v>414590</v>
       </c>
       <c r="R18" t="n">
-        <v>6840383</v>
+        <v>6840200</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2545,7 +2541,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,7 +2551,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,13 +2577,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552349</t>
+          <t>https://artportalen.se/Sighting/135552371</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135552371</v>
+        <v>135552372</v>
       </c>
       <c r="B19" t="n">
         <v>92153</v>
@@ -2622,13 +2618,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>414590</v>
+        <v>414593</v>
       </c>
       <c r="R19" t="n">
-        <v>6840200</v>
+        <v>6840201</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,7 +2663,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,13 +2689,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552371</t>
+          <t>https://artportalen.se/Sighting/135552372</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135552372</v>
+        <v>135552384</v>
       </c>
       <c r="B20" t="n">
         <v>92153</v>
@@ -2734,13 +2730,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>414593</v>
+        <v>414637</v>
       </c>
       <c r="R20" t="n">
-        <v>6840201</v>
+        <v>6840257</v>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2779,7 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,13 +2801,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552372</t>
+          <t>https://artportalen.se/Sighting/135552384</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135552384</v>
+        <v>135552385</v>
       </c>
       <c r="B21" t="n">
         <v>92153</v>
@@ -2846,13 +2842,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>414637</v>
+        <v>414591</v>
       </c>
       <c r="R21" t="n">
-        <v>6840257</v>
+        <v>6840230</v>
       </c>
       <c r="S21" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2881,7 +2877,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2891,7 +2887,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,38 +2913,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552384</t>
+          <t>https://artportalen.se/Sighting/135552385</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135552385</v>
+        <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92153</v>
+        <v>92027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2958,13 +2954,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>414591</v>
+        <v>414626</v>
       </c>
       <c r="R22" t="n">
-        <v>6840230</v>
+        <v>6840401</v>
       </c>
       <c r="S22" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2993,7 +2989,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3003,7 +2999,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,38 +3025,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552385</t>
+          <t>https://artportalen.se/Sighting/135552348</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135552348</v>
+        <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>92027</v>
+        <v>91937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3070,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>414626</v>
+        <v>414651</v>
       </c>
       <c r="R23" t="n">
-        <v>6840401</v>
+        <v>6840334</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3105,7 +3101,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3115,7 +3111,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,38 +3137,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552348</t>
+          <t>https://artportalen.se/Sighting/135552342</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135552342</v>
+        <v>135552338</v>
       </c>
       <c r="B24" t="n">
-        <v>91937</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3182,13 +3178,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>414651</v>
+        <v>414675</v>
       </c>
       <c r="R24" t="n">
-        <v>6840334</v>
+        <v>6840320</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3227,7 +3223,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,13 +3249,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552342</t>
+          <t>https://artportalen.se/Sighting/135552338</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135552338</v>
+        <v>135552344</v>
       </c>
       <c r="B25" t="n">
         <v>78776</v>
@@ -3294,13 +3290,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>414675</v>
+        <v>414654</v>
       </c>
       <c r="R25" t="n">
-        <v>6840320</v>
+        <v>6840390</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3325,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3335,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3365,13 +3361,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552338</t>
+          <t>https://artportalen.se/Sighting/135552344</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135552344</v>
+        <v>135552361</v>
       </c>
       <c r="B26" t="n">
         <v>78776</v>
@@ -3406,13 +3402,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>414654</v>
+        <v>414577</v>
       </c>
       <c r="R26" t="n">
-        <v>6840390</v>
+        <v>6840369</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3441,7 +3437,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3451,7 +3447,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3477,13 +3473,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552344</t>
+          <t>https://artportalen.se/Sighting/135552361</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135552361</v>
+        <v>135552366</v>
       </c>
       <c r="B27" t="n">
         <v>78776</v>
@@ -3518,10 +3514,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>414577</v>
+        <v>414606</v>
       </c>
       <c r="R27" t="n">
-        <v>6840369</v>
+        <v>6840293</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3553,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3563,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3589,13 +3585,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552361</t>
+          <t>https://artportalen.se/Sighting/135552366</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135552366</v>
+        <v>135552369</v>
       </c>
       <c r="B28" t="n">
         <v>78776</v>
@@ -3630,13 +3626,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>414606</v>
+        <v>414575</v>
       </c>
       <c r="R28" t="n">
-        <v>6840293</v>
+        <v>6840232</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3665,7 +3661,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3675,7 +3671,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,13 +3697,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552366</t>
+          <t>https://artportalen.se/Sighting/135552369</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135552369</v>
+        <v>135552376</v>
       </c>
       <c r="B29" t="n">
         <v>78776</v>
@@ -3742,13 +3738,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>414575</v>
+        <v>414635</v>
       </c>
       <c r="R29" t="n">
-        <v>6840232</v>
+        <v>6840234</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3777,7 +3773,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3783,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,13 +3809,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552369</t>
+          <t>https://artportalen.se/Sighting/135552376</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135552376</v>
+        <v>135552388</v>
       </c>
       <c r="B30" t="n">
         <v>78776</v>
@@ -3854,13 +3850,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>414635</v>
+        <v>414554</v>
       </c>
       <c r="R30" t="n">
-        <v>6840234</v>
+        <v>6840205</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3889,7 +3885,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3899,7 +3895,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,13 +3921,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552376</t>
+          <t>https://artportalen.se/Sighting/135552388</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135552388</v>
+        <v>135552394</v>
       </c>
       <c r="B31" t="n">
         <v>78776</v>
@@ -3966,13 +3962,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>414554</v>
+        <v>414567</v>
       </c>
       <c r="R31" t="n">
-        <v>6840205</v>
+        <v>6840142</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4001,7 +3997,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4011,7 +4007,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,16 +4033,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552388</t>
+          <t>https://artportalen.se/Sighting/135552394</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135552394</v>
+        <v>129688126</v>
       </c>
       <c r="B32" t="n">
-        <v>78776</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,37 +4050,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Plantbygget, Dlr</t>
+          <t>Storbäcksvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>414567</v>
+        <v>414608</v>
       </c>
       <c r="R32" t="n">
-        <v>6840142</v>
+        <v>6840207</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4108,22 +4108,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:19</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21:19</t>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4138,27 +4133,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552394</t>
+          <t>https://artportalen.se/Sighting/129688126</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129688126</v>
+        <v>135552340</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,24 +4178,20 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>414608</v>
+        <v>414679</v>
       </c>
       <c r="R33" t="n">
-        <v>6840207</v>
+        <v>6840324</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4224,17 +4215,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,27 +4245,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129688126</t>
+          <t>https://artportalen.se/Sighting/135552340</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135552340</v>
+        <v>135552347</v>
       </c>
       <c r="B34" t="n">
-        <v>79130</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4277,21 +4273,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4301,13 +4297,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>414679</v>
+        <v>414608</v>
       </c>
       <c r="R34" t="n">
-        <v>6840324</v>
+        <v>6840392</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4336,7 +4332,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4346,7 +4342,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,13 +4368,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552340</t>
+          <t>https://artportalen.se/Sighting/135552347</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135552347</v>
+        <v>135552352</v>
       </c>
       <c r="B35" t="n">
         <v>79992</v>
@@ -4413,13 +4409,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>414608</v>
+        <v>414600</v>
       </c>
       <c r="R35" t="n">
-        <v>6840392</v>
+        <v>6840351</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4448,7 +4444,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4458,7 +4454,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4484,13 +4480,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552347</t>
+          <t>https://artportalen.se/Sighting/135552352</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135552352</v>
+        <v>135552360</v>
       </c>
       <c r="B36" t="n">
         <v>79992</v>
@@ -4525,13 +4521,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>414600</v>
+        <v>414559</v>
       </c>
       <c r="R36" t="n">
-        <v>6840351</v>
+        <v>6840378</v>
       </c>
       <c r="S36" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4560,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4570,7 +4566,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,13 +4592,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552352</t>
+          <t>https://artportalen.se/Sighting/135552360</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135552360</v>
+        <v>135552367</v>
       </c>
       <c r="B37" t="n">
         <v>79992</v>
@@ -4637,13 +4633,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>414559</v>
+        <v>414590</v>
       </c>
       <c r="R37" t="n">
-        <v>6840378</v>
+        <v>6840249</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4672,7 +4668,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4682,7 +4678,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4708,13 +4704,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552360</t>
+          <t>https://artportalen.se/Sighting/135552367</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135552367</v>
+        <v>135552377</v>
       </c>
       <c r="B38" t="n">
         <v>79992</v>
@@ -4749,10 +4745,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>414590</v>
+        <v>414636</v>
       </c>
       <c r="R38" t="n">
-        <v>6840249</v>
+        <v>6840234</v>
       </c>
       <c r="S38" t="n">
         <v>8</v>
@@ -4784,7 +4780,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4794,7 +4790,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4820,13 +4816,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552367</t>
+          <t>https://artportalen.se/Sighting/135552377</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135552377</v>
+        <v>135552378</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4861,10 +4857,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>414636</v>
+        <v>414643</v>
       </c>
       <c r="R39" t="n">
-        <v>6840234</v>
+        <v>6840239</v>
       </c>
       <c r="S39" t="n">
         <v>8</v>
@@ -4932,13 +4928,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552377</t>
+          <t>https://artportalen.se/Sighting/135552378</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135552378</v>
+        <v>135552380</v>
       </c>
       <c r="B40" t="n">
         <v>79992</v>
@@ -4973,13 +4969,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>414643</v>
+        <v>414673</v>
       </c>
       <c r="R40" t="n">
-        <v>6840239</v>
+        <v>6840258</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5008,7 +5004,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5018,7 +5014,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5044,13 +5040,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552378</t>
+          <t>https://artportalen.se/Sighting/135552380</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135552380</v>
+        <v>135552382</v>
       </c>
       <c r="B41" t="n">
         <v>79992</v>
@@ -5085,13 +5081,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>414673</v>
+        <v>414668</v>
       </c>
       <c r="R41" t="n">
-        <v>6840258</v>
+        <v>6840259</v>
       </c>
       <c r="S41" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5156,16 +5152,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552380</t>
+          <t>https://artportalen.se/Sighting/135552382</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135552382</v>
+        <v>135552362</v>
       </c>
       <c r="B42" t="n">
-        <v>79992</v>
+        <v>78377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,21 +5169,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5197,13 +5193,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>414668</v>
+        <v>414577</v>
       </c>
       <c r="R42" t="n">
-        <v>6840259</v>
+        <v>6840367</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,7 +5228,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5242,7 +5238,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5268,13 +5264,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552382</t>
+          <t>https://artportalen.se/Sighting/135552362</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135552362</v>
+        <v>135552368</v>
       </c>
       <c r="B43" t="n">
         <v>78377</v>
@@ -5309,13 +5305,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>414577</v>
+        <v>414574</v>
       </c>
       <c r="R43" t="n">
-        <v>6840367</v>
+        <v>6840234</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5344,7 +5340,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5354,7 +5350,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5380,13 +5376,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552362</t>
+          <t>https://artportalen.se/Sighting/135552368</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135552368</v>
+        <v>135552387</v>
       </c>
       <c r="B44" t="n">
         <v>78377</v>
@@ -5421,13 +5417,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>414574</v>
+        <v>414557</v>
       </c>
       <c r="R44" t="n">
-        <v>6840234</v>
+        <v>6840202</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5456,7 +5452,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5466,7 +5462,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,13 +5488,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552368</t>
+          <t>https://artportalen.se/Sighting/135552387</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135552387</v>
+        <v>135552391</v>
       </c>
       <c r="B45" t="n">
         <v>78377</v>
@@ -5533,13 +5529,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>414557</v>
+        <v>414545</v>
       </c>
       <c r="R45" t="n">
-        <v>6840202</v>
+        <v>6840174</v>
       </c>
       <c r="S45" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5568,7 +5564,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5578,7 +5574,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5604,13 +5600,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552387</t>
+          <t>https://artportalen.se/Sighting/135552391</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135552391</v>
+        <v>135552393</v>
       </c>
       <c r="B46" t="n">
         <v>78377</v>
@@ -5645,13 +5641,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>414545</v>
+        <v>414567</v>
       </c>
       <c r="R46" t="n">
-        <v>6840174</v>
+        <v>6840142</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5680,7 +5676,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5690,7 +5686,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5716,38 +5712,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552391</t>
+          <t>https://artportalen.se/Sighting/135552393</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135552393</v>
+        <v>135552359</v>
       </c>
       <c r="B47" t="n">
-        <v>78377</v>
+        <v>58848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6487</v>
+        <v>208242</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5757,13 +5753,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>414567</v>
+        <v>414524</v>
       </c>
       <c r="R47" t="n">
-        <v>6840142</v>
+        <v>6840378</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5792,7 +5788,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5802,7 +5798,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5828,54 +5824,58 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552393</t>
+          <t>https://artportalen.se/Sighting/135552359</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135552359</v>
+        <v>129688125</v>
       </c>
       <c r="B48" t="n">
-        <v>58848</v>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208242</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Plantbygget, Dlr</t>
+          <t>Storbäcksvallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>414524</v>
+        <v>414605</v>
       </c>
       <c r="R48" t="n">
-        <v>6840378</v>
+        <v>6840213</v>
       </c>
       <c r="S48" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5899,22 +5899,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>20:47</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>20:47</t>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5929,27 +5924,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552359</t>
+          <t>https://artportalen.se/Sighting/129688125</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129688125</v>
+        <v>135552353</v>
       </c>
       <c r="B49" t="n">
-        <v>79085</v>
+        <v>79131</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5974,24 +5969,20 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>414605</v>
+        <v>414594</v>
       </c>
       <c r="R49" t="n">
-        <v>6840213</v>
+        <v>6840343</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6015,17 +6006,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6040,24 +6036,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129688125</t>
+          <t>https://artportalen.se/Sighting/135552353</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135552353</v>
+        <v>135552374</v>
       </c>
       <c r="B50" t="n">
         <v>79131</v>
@@ -6092,13 +6088,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>414594</v>
+        <v>414602</v>
       </c>
       <c r="R50" t="n">
-        <v>6840343</v>
+        <v>6840210</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6127,7 +6123,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6137,7 +6133,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,13 +6159,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552353</t>
+          <t>https://artportalen.se/Sighting/135552374</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135552374</v>
+        <v>135552375</v>
       </c>
       <c r="B51" t="n">
         <v>79131</v>
@@ -6204,13 +6200,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>414602</v>
+        <v>414607</v>
       </c>
       <c r="R51" t="n">
-        <v>6840210</v>
+        <v>6840232</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6239,7 +6235,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6249,7 +6245,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6275,13 +6271,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552374</t>
+          <t>https://artportalen.se/Sighting/135552375</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135552375</v>
+        <v>135552389</v>
       </c>
       <c r="B52" t="n">
         <v>79131</v>
@@ -6316,13 +6312,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>414607</v>
+        <v>414554</v>
       </c>
       <c r="R52" t="n">
-        <v>6840232</v>
+        <v>6840204</v>
       </c>
       <c r="S52" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6351,7 +6347,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6361,7 +6357,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6387,16 +6383,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552375</t>
+          <t>https://artportalen.se/Sighting/135552389</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135552389</v>
+        <v>135552339</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>79963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6404,21 +6400,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6428,13 +6424,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>414554</v>
+        <v>414685</v>
       </c>
       <c r="R53" t="n">
-        <v>6840204</v>
+        <v>6840332</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6463,7 +6459,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6473,7 +6469,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6499,13 +6495,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552389</t>
+          <t>https://artportalen.se/Sighting/135552339</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135552339</v>
+        <v>135552343</v>
       </c>
       <c r="B54" t="n">
         <v>79963</v>
@@ -6540,13 +6536,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>414685</v>
+        <v>414649</v>
       </c>
       <c r="R54" t="n">
-        <v>6840332</v>
+        <v>6840383</v>
       </c>
       <c r="S54" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6575,7 +6571,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6585,7 +6581,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6611,13 +6607,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552339</t>
+          <t>https://artportalen.se/Sighting/135552343</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135552343</v>
+        <v>135552355</v>
       </c>
       <c r="B55" t="n">
         <v>79963</v>
@@ -6652,13 +6648,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>414649</v>
+        <v>414564</v>
       </c>
       <c r="R55" t="n">
-        <v>6840383</v>
+        <v>6840341</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6687,7 +6683,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6697,7 +6693,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6723,13 +6719,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552343</t>
+          <t>https://artportalen.se/Sighting/135552355</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135552355</v>
+        <v>135552356</v>
       </c>
       <c r="B56" t="n">
         <v>79963</v>
@@ -6764,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>414564</v>
+        <v>414524</v>
       </c>
       <c r="R56" t="n">
-        <v>6840341</v>
+        <v>6840332</v>
       </c>
       <c r="S56" t="n">
         <v>13</v>
@@ -6799,7 +6795,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6809,7 +6805,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6835,13 +6831,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552355</t>
+          <t>https://artportalen.se/Sighting/135552356</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135552356</v>
+        <v>135552363</v>
       </c>
       <c r="B57" t="n">
         <v>79963</v>
@@ -6876,13 +6872,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>414524</v>
+        <v>414577</v>
       </c>
       <c r="R57" t="n">
-        <v>6840332</v>
+        <v>6840367</v>
       </c>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6911,7 +6907,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6921,7 +6917,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6947,13 +6943,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552356</t>
+          <t>https://artportalen.se/Sighting/135552363</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135552363</v>
+        <v>135552370</v>
       </c>
       <c r="B58" t="n">
         <v>79963</v>
@@ -6988,13 +6984,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>414577</v>
+        <v>414573</v>
       </c>
       <c r="R58" t="n">
-        <v>6840367</v>
+        <v>6840230</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7023,7 +7019,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7033,7 +7029,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7059,13 +7055,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552363</t>
+          <t>https://artportalen.se/Sighting/135552370</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135552370</v>
+        <v>135552373</v>
       </c>
       <c r="B59" t="n">
         <v>79963</v>
@@ -7100,13 +7096,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>414573</v>
+        <v>414604</v>
       </c>
       <c r="R59" t="n">
         <v>6840230</v>
       </c>
       <c r="S59" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7135,7 +7131,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7145,7 +7141,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7171,13 +7167,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552370</t>
+          <t>https://artportalen.se/Sighting/135552373</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135552373</v>
+        <v>135552383</v>
       </c>
       <c r="B60" t="n">
         <v>79963</v>
@@ -7212,13 +7208,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>414604</v>
+        <v>414668</v>
       </c>
       <c r="R60" t="n">
-        <v>6840230</v>
+        <v>6840259</v>
       </c>
       <c r="S60" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7247,7 +7243,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7257,7 +7253,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7283,13 +7279,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135552373</t>
+          <t>https://artportalen.se/Sighting/135552383</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135552383</v>
+        <v>135552392</v>
       </c>
       <c r="B61" t="n">
         <v>79963</v>
@@ -7324,10 +7320,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>414668</v>
+        <v>414564</v>
       </c>
       <c r="R61" t="n">
-        <v>6840259</v>
+        <v>6840146</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7359,7 +7355,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7369,7 +7365,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7394,118 +7390,6 @@
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135552383</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135552392</v>
-      </c>
-      <c r="B62" t="n">
-        <v>79963</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Plantbygget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>414564</v>
-      </c>
-      <c r="R62" t="n">
-        <v>6840146</v>
-      </c>
-      <c r="S62" t="n">
-        <v>5</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Särna</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>21:18</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>21:18</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Moa Björnberg Dillner</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Moa Björnberg Dillner</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135552392</t>
         </is>
@@ -7573,7 +7457,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135552336</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135552337</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135552341</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135552346</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135552350</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135552351</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135552354</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135552357</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135552364</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135552365</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135552379</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135552390</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135552381</v>
       </c>
       <c r="B15" t="n">
-        <v>79468</v>
+        <v>79506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135552371</v>
       </c>
       <c r="B18" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>135552372</v>
       </c>
       <c r="B19" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>135552384</v>
       </c>
       <c r="B20" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135552385</v>
       </c>
       <c r="B21" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135552338</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>135552344</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135552361</v>
       </c>
       <c r="B26" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135552366</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>135552369</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>135552376</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>135552388</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>135552394</v>
       </c>
       <c r="B31" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>135552340</v>
       </c>
       <c r="B33" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>135552347</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>135552352</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>135552360</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>135552367</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>135552377</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135552378</v>
       </c>
       <c r="B39" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135552380</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135552382</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>135552362</v>
       </c>
       <c r="B42" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135552368</v>
       </c>
       <c r="B43" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>135552387</v>
       </c>
       <c r="B44" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135552391</v>
       </c>
       <c r="B45" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>135552393</v>
       </c>
       <c r="B46" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>135552359</v>
       </c>
       <c r="B47" t="n">
-        <v>58848</v>
+        <v>58853</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135552353</v>
       </c>
       <c r="B49" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135552374</v>
       </c>
       <c r="B50" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135552375</v>
       </c>
       <c r="B51" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>135552389</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135552339</v>
       </c>
       <c r="B53" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>135552343</v>
       </c>
       <c r="B54" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>135552355</v>
       </c>
       <c r="B55" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>135552356</v>
       </c>
       <c r="B56" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>135552363</v>
       </c>
       <c r="B57" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>135552370</v>
       </c>
       <c r="B58" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>135552373</v>
       </c>
       <c r="B59" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>135552383</v>
       </c>
       <c r="B60" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>135552392</v>
       </c>
       <c r="B61" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135552336</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135552337</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135552341</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135552346</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135552350</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135552351</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135552354</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135552357</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135552364</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135552365</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135552379</v>
       </c>
       <c r="B13" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135552390</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135552381</v>
       </c>
       <c r="B15" t="n">
-        <v>79506</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135552371</v>
       </c>
       <c r="B18" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>135552372</v>
       </c>
       <c r="B19" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>135552384</v>
       </c>
       <c r="B20" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135552385</v>
       </c>
       <c r="B21" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135552338</v>
       </c>
       <c r="B24" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>135552344</v>
       </c>
       <c r="B25" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135552361</v>
       </c>
       <c r="B26" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135552366</v>
       </c>
       <c r="B27" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>135552369</v>
       </c>
       <c r="B28" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>135552376</v>
       </c>
       <c r="B29" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>135552388</v>
       </c>
       <c r="B30" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>135552394</v>
       </c>
       <c r="B31" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>135552340</v>
       </c>
       <c r="B33" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>135552347</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>135552352</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>135552360</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>135552367</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>135552377</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135552378</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135552380</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135552382</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>135552362</v>
       </c>
       <c r="B42" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135552368</v>
       </c>
       <c r="B43" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>135552387</v>
       </c>
       <c r="B44" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135552391</v>
       </c>
       <c r="B45" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>135552393</v>
       </c>
       <c r="B46" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135552353</v>
       </c>
       <c r="B49" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135552374</v>
       </c>
       <c r="B50" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135552375</v>
       </c>
       <c r="B51" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>135552389</v>
       </c>
       <c r="B52" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135552339</v>
       </c>
       <c r="B53" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>135552343</v>
       </c>
       <c r="B54" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>135552355</v>
       </c>
       <c r="B55" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>135552356</v>
       </c>
       <c r="B56" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>135552363</v>
       </c>
       <c r="B57" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>135552370</v>
       </c>
       <c r="B58" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>135552373</v>
       </c>
       <c r="B59" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>135552383</v>
       </c>
       <c r="B60" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>135552392</v>
       </c>
       <c r="B61" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688124</v>
+        <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92083</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414613</v>
+        <v>414506</v>
       </c>
       <c r="R2" t="n">
-        <v>6840353</v>
+        <v>6840350</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129688124</t>
+          <t>https://artportalen.se/Sighting/135552358</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688126</v>
+        <v>135552336</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,41 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>414608</v>
+        <v>414690</v>
       </c>
       <c r="R3" t="n">
-        <v>6840207</v>
+        <v>6840294</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129688126</t>
+          <t>https://artportalen.se/Sighting/135552336</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688125</v>
+        <v>135552337</v>
       </c>
       <c r="B4" t="n">
-        <v>79085</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,41 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storbäcksvallen, Dlr</t>
+          <t>Plantbygget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414605</v>
+        <v>414697</v>
       </c>
       <c r="R4" t="n">
-        <v>6840213</v>
+        <v>6840323</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,18 +999,6399 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135552337</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135552341</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>414653</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6840340</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552341</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135552346</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>414623</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6840405</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552346</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135552350</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>414609</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6840382</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552350</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135552351</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>414601</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6840335</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552351</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135552354</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>414588</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6840341</v>
+      </c>
+      <c r="S9" t="n">
+        <v>28</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552354</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135552357</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>414522</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6840327</v>
+      </c>
+      <c r="S10" t="n">
+        <v>16</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552357</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135552364</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>353</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>414591</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6840303</v>
+      </c>
+      <c r="S11" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552364</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135552365</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>414601</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6840307</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552365</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135552379</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>414643</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6840242</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552379</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135552390</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>353</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>414552</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6840177</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552390</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135552381</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>967</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>414671</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6840258</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552381</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129688124</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storbäcksvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>414613</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6840353</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688124</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135552349</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>414617</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6840383</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552349</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135552371</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>414590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6840200</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552371</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135552372</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>414593</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6840201</v>
+      </c>
+      <c r="S19" t="n">
+        <v>22</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552372</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135552384</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>414637</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6840257</v>
+      </c>
+      <c r="S20" t="n">
+        <v>19</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552384</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135552385</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>414591</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6840230</v>
+      </c>
+      <c r="S21" t="n">
+        <v>49</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552385</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135552348</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>414626</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6840401</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552348</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135552342</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>414651</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6840334</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552342</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135552338</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>414675</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6840320</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552338</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135552344</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>414654</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6840390</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552344</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135552361</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>414577</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6840369</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552361</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135552366</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>414606</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6840293</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552366</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135552369</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>414575</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6840232</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552369</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135552376</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>414635</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6840234</v>
+      </c>
+      <c r="S29" t="n">
+        <v>14</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552376</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135552388</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>414554</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6840205</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552388</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135552394</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>414567</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6840142</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552394</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129688126</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storbäcksvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>414608</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6840207</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688126</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135552340</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>414679</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6840324</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552340</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135552347</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>414608</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6840392</v>
+      </c>
+      <c r="S34" t="n">
+        <v>14</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552347</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135552352</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>414600</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6840351</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552352</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135552360</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>414559</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6840378</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552360</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135552367</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>414590</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6840249</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552367</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135552377</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>414636</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6840234</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552377</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135552378</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>414643</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6840239</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552378</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135552380</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>414673</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6840258</v>
+      </c>
+      <c r="S40" t="n">
+        <v>24</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552380</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135552382</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>414668</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6840259</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552382</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135552362</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>414577</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6840367</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552362</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135552368</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>414574</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6840234</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552368</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135552387</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>414557</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6840202</v>
+      </c>
+      <c r="S44" t="n">
+        <v>17</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552387</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135552391</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>414545</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6840174</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552391</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135552393</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>414567</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6840142</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552393</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135552359</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58853</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>414524</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6840378</v>
+      </c>
+      <c r="S47" t="n">
+        <v>22</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552359</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129688125</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storbäcksvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>414605</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6840213</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129688125</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135552353</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>414594</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6840343</v>
+      </c>
+      <c r="S49" t="n">
+        <v>11</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552353</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135552374</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>414602</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6840210</v>
+      </c>
+      <c r="S50" t="n">
+        <v>9</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552374</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135552375</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>414607</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6840232</v>
+      </c>
+      <c r="S51" t="n">
+        <v>22</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552375</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135552389</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>414554</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6840204</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552389</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135552339</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>414685</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6840332</v>
+      </c>
+      <c r="S53" t="n">
+        <v>16</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552339</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135552343</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>414649</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6840383</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552343</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135552355</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>414564</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6840341</v>
+      </c>
+      <c r="S55" t="n">
+        <v>13</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552355</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135552356</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>414524</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6840332</v>
+      </c>
+      <c r="S56" t="n">
+        <v>13</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552356</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135552363</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>414577</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6840367</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552363</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135552370</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>414573</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6840230</v>
+      </c>
+      <c r="S58" t="n">
+        <v>24</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552370</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135552373</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>414604</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6840230</v>
+      </c>
+      <c r="S59" t="n">
+        <v>16</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552373</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135552383</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>414668</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6840259</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552383</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135552392</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Plantbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>414564</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6840146</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135552392</t>
         </is>
       </c>
     </row>
@@ -1016,6 +7400,63 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135552371</v>
       </c>
       <c r="B18" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>135552372</v>
       </c>
       <c r="B19" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>135552384</v>
       </c>
       <c r="B20" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135552385</v>
       </c>
       <c r="B21" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135552336</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135552337</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135552341</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135552346</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135552350</v>
       </c>
       <c r="B7" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135552351</v>
       </c>
       <c r="B8" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135552354</v>
       </c>
       <c r="B9" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135552357</v>
       </c>
       <c r="B10" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135552364</v>
       </c>
       <c r="B11" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135552365</v>
       </c>
       <c r="B12" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135552379</v>
       </c>
       <c r="B13" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135552390</v>
       </c>
       <c r="B14" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135552381</v>
       </c>
       <c r="B15" t="n">
-        <v>79536</v>
+        <v>79538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135552371</v>
       </c>
       <c r="B18" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>135552372</v>
       </c>
       <c r="B19" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>135552384</v>
       </c>
       <c r="B20" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135552385</v>
       </c>
       <c r="B21" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135552338</v>
       </c>
       <c r="B24" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>135552344</v>
       </c>
       <c r="B25" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135552361</v>
       </c>
       <c r="B26" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135552366</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>135552369</v>
       </c>
       <c r="B28" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>135552376</v>
       </c>
       <c r="B29" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>135552388</v>
       </c>
       <c r="B30" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>135552394</v>
       </c>
       <c r="B31" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>135552340</v>
       </c>
       <c r="B33" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>135552347</v>
       </c>
       <c r="B34" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>135552352</v>
       </c>
       <c r="B35" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>135552360</v>
       </c>
       <c r="B36" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>135552367</v>
       </c>
       <c r="B37" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>135552377</v>
       </c>
       <c r="B38" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135552378</v>
       </c>
       <c r="B39" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135552380</v>
       </c>
       <c r="B40" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135552382</v>
       </c>
       <c r="B41" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>135552362</v>
       </c>
       <c r="B42" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135552368</v>
       </c>
       <c r="B43" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>135552387</v>
       </c>
       <c r="B44" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135552391</v>
       </c>
       <c r="B45" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>135552393</v>
       </c>
       <c r="B46" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>135552359</v>
       </c>
       <c r="B47" t="n">
-        <v>58853</v>
+        <v>58855</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135552353</v>
       </c>
       <c r="B49" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135552374</v>
       </c>
       <c r="B50" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135552375</v>
       </c>
       <c r="B51" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>135552389</v>
       </c>
       <c r="B52" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135552339</v>
       </c>
       <c r="B53" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>135552343</v>
       </c>
       <c r="B54" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>135552355</v>
       </c>
       <c r="B55" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>135552356</v>
       </c>
       <c r="B56" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>135552363</v>
       </c>
       <c r="B57" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>135552370</v>
       </c>
       <c r="B58" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>135552373</v>
       </c>
       <c r="B59" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>135552383</v>
       </c>
       <c r="B60" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>135552392</v>
       </c>
       <c r="B61" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135552336</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135552337</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135552341</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135552346</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135552350</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135552351</v>
       </c>
       <c r="B8" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135552354</v>
       </c>
       <c r="B9" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135552357</v>
       </c>
       <c r="B10" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135552364</v>
       </c>
       <c r="B11" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135552365</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135552379</v>
       </c>
       <c r="B13" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135552390</v>
       </c>
       <c r="B14" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135552381</v>
       </c>
       <c r="B15" t="n">
-        <v>79538</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135552371</v>
       </c>
       <c r="B18" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>135552372</v>
       </c>
       <c r="B19" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>135552384</v>
       </c>
       <c r="B20" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135552385</v>
       </c>
       <c r="B21" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135552338</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>135552344</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>135552361</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135552366</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>135552369</v>
       </c>
       <c r="B28" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>135552376</v>
       </c>
       <c r="B29" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>135552388</v>
       </c>
       <c r="B30" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>135552394</v>
       </c>
       <c r="B31" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>135552340</v>
       </c>
       <c r="B33" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>135552347</v>
       </c>
       <c r="B34" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>135552352</v>
       </c>
       <c r="B35" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>135552360</v>
       </c>
       <c r="B36" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>135552367</v>
       </c>
       <c r="B37" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>135552377</v>
       </c>
       <c r="B38" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135552378</v>
       </c>
       <c r="B39" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>135552380</v>
       </c>
       <c r="B40" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135552382</v>
       </c>
       <c r="B41" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>135552362</v>
       </c>
       <c r="B42" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135552368</v>
       </c>
       <c r="B43" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>135552387</v>
       </c>
       <c r="B44" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135552391</v>
       </c>
       <c r="B45" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>135552393</v>
       </c>
       <c r="B46" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>135552353</v>
       </c>
       <c r="B49" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>135552374</v>
       </c>
       <c r="B50" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>135552375</v>
       </c>
       <c r="B51" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>135552389</v>
       </c>
       <c r="B52" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135552339</v>
       </c>
       <c r="B53" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>135552343</v>
       </c>
       <c r="B54" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>135552355</v>
       </c>
       <c r="B55" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>135552356</v>
       </c>
       <c r="B56" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>135552363</v>
       </c>
       <c r="B57" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>135552370</v>
       </c>
       <c r="B58" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>135552373</v>
       </c>
       <c r="B59" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>135552383</v>
       </c>
       <c r="B60" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>135552392</v>
       </c>
       <c r="B61" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30101-2026 artfynd.xlsx
+++ b/artfynd/A 30101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135552358</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135552349</v>
       </c>
       <c r="B17" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>135552371</v>
       </c>
       <c r="B18" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>135552372</v>
       </c>
       <c r="B19" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>135552384</v>
       </c>
       <c r="B20" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135552385</v>
       </c>
       <c r="B21" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135552348</v>
       </c>
       <c r="B22" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135552342</v>
       </c>
       <c r="B23" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
